--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>113258470</v>
       </c>
       <c r="B13" t="n">
-        <v>95574</v>
+        <v>95590</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>113288922</v>
       </c>
       <c r="B14" t="n">
-        <v>56658</v>
+        <v>56657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399393</v>
+        <v>113399391</v>
       </c>
       <c r="B15" t="n">
         <v>56781</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318057</v>
+        <v>318054</v>
       </c>
       <c r="R15" t="n">
-        <v>6444564</v>
+        <v>6444671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2441,7 +2441,7 @@
         <v>113399385</v>
       </c>
       <c r="B16" t="n">
-        <v>95574</v>
+        <v>95590</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>113399383</v>
       </c>
       <c r="B17" t="n">
-        <v>95574</v>
+        <v>95590</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399391</v>
+        <v>113399386</v>
       </c>
       <c r="B18" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318054</v>
+        <v>318032</v>
       </c>
       <c r="R18" t="n">
-        <v>6444671</v>
+        <v>6444666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,11 +2718,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399386</v>
+        <v>113399393</v>
       </c>
       <c r="B19" t="n">
-        <v>95574</v>
+        <v>56781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2789,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318032</v>
+        <v>318057</v>
       </c>
       <c r="R19" t="n">
-        <v>6444666</v>
+        <v>6444564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2825,6 +2820,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,7 +2854,7 @@
         <v>113399384</v>
       </c>
       <c r="B20" t="n">
-        <v>95574</v>
+        <v>95590</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,7 +2331,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399391</v>
+        <v>113399393</v>
       </c>
       <c r="B15" t="n">
         <v>56781</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318054</v>
+        <v>318057</v>
       </c>
       <c r="R15" t="n">
-        <v>6444671</v>
+        <v>6444564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399385</v>
+        <v>113399383</v>
       </c>
       <c r="B16" t="n">
         <v>95590</v>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318027</v>
+        <v>317945</v>
       </c>
       <c r="R16" t="n">
-        <v>6444643</v>
+        <v>6444452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399383</v>
+        <v>113399386</v>
       </c>
       <c r="B17" t="n">
         <v>95590</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>317945</v>
+        <v>318032</v>
       </c>
       <c r="R17" t="n">
-        <v>6444452</v>
+        <v>6444666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399386</v>
+        <v>113399385</v>
       </c>
       <c r="B18" t="n">
         <v>95590</v>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318032</v>
+        <v>318027</v>
       </c>
       <c r="R18" t="n">
-        <v>6444666</v>
+        <v>6444643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399393</v>
+        <v>113399384</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>95590</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318057</v>
+        <v>318059</v>
       </c>
       <c r="R19" t="n">
-        <v>6444564</v>
+        <v>6444586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,11 +2820,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399384</v>
+        <v>113399391</v>
       </c>
       <c r="B20" t="n">
-        <v>95590</v>
+        <v>56781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,25 +2858,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318059</v>
+        <v>318054</v>
       </c>
       <c r="R20" t="n">
-        <v>6444586</v>
+        <v>6444671</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2927,6 +2922,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>113258470</v>
       </c>
       <c r="B13" t="n">
-        <v>95590</v>
+        <v>95602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>113288922</v>
       </c>
       <c r="B14" t="n">
-        <v>56657</v>
+        <v>56658</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399393</v>
+        <v>113399391</v>
       </c>
       <c r="B15" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318057</v>
+        <v>318054</v>
       </c>
       <c r="R15" t="n">
-        <v>6444564</v>
+        <v>6444671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399383</v>
+        <v>113399384</v>
       </c>
       <c r="B16" t="n">
-        <v>95590</v>
+        <v>95602</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>317945</v>
+        <v>318059</v>
       </c>
       <c r="R16" t="n">
-        <v>6444452</v>
+        <v>6444586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399386</v>
+        <v>113399385</v>
       </c>
       <c r="B17" t="n">
-        <v>95590</v>
+        <v>95602</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318032</v>
+        <v>318027</v>
       </c>
       <c r="R17" t="n">
-        <v>6444666</v>
+        <v>6444643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399385</v>
+        <v>113399386</v>
       </c>
       <c r="B18" t="n">
-        <v>95590</v>
+        <v>95602</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318027</v>
+        <v>318032</v>
       </c>
       <c r="R18" t="n">
-        <v>6444643</v>
+        <v>6444666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399384</v>
+        <v>113399393</v>
       </c>
       <c r="B19" t="n">
-        <v>95590</v>
+        <v>56782</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318059</v>
+        <v>318057</v>
       </c>
       <c r="R19" t="n">
-        <v>6444586</v>
+        <v>6444564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,6 +2820,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399391</v>
+        <v>113399383</v>
       </c>
       <c r="B20" t="n">
-        <v>56781</v>
+        <v>95602</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2858,25 +2863,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318054</v>
+        <v>317945</v>
       </c>
       <c r="R20" t="n">
-        <v>6444671</v>
+        <v>6444452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,11 +2927,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>113411940</v>
       </c>
       <c r="B21" t="n">
-        <v>56656</v>
+        <v>56657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399391</v>
+        <v>113399385</v>
       </c>
       <c r="B15" t="n">
-        <v>56782</v>
+        <v>95602</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318054</v>
+        <v>318027</v>
       </c>
       <c r="R15" t="n">
-        <v>6444671</v>
+        <v>6444643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,11 +2407,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2540,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399385</v>
+        <v>113399391</v>
       </c>
       <c r="B17" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2552,25 +2547,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318027</v>
+        <v>318054</v>
       </c>
       <c r="R17" t="n">
-        <v>6444643</v>
+        <v>6444671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2616,6 +2611,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399386</v>
+        <v>113399393</v>
       </c>
       <c r="B18" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318032</v>
+        <v>318057</v>
       </c>
       <c r="R18" t="n">
-        <v>6444666</v>
+        <v>6444564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,6 +2718,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399393</v>
+        <v>113399386</v>
       </c>
       <c r="B19" t="n">
-        <v>56782</v>
+        <v>95602</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,25 +2761,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2784,10 +2789,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318057</v>
+        <v>318032</v>
       </c>
       <c r="R19" t="n">
-        <v>6444564</v>
+        <v>6444666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,11 +2825,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>113258470</v>
       </c>
       <c r="B13" t="n">
-        <v>95602</v>
+        <v>95624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>113288922</v>
       </c>
       <c r="B14" t="n">
-        <v>56658</v>
+        <v>56659</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399385</v>
+        <v>113399386</v>
       </c>
       <c r="B15" t="n">
-        <v>95602</v>
+        <v>95624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318027</v>
+        <v>318032</v>
       </c>
       <c r="R15" t="n">
-        <v>6444643</v>
+        <v>6444666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399384</v>
+        <v>113399383</v>
       </c>
       <c r="B16" t="n">
-        <v>95602</v>
+        <v>95624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318059</v>
+        <v>317945</v>
       </c>
       <c r="R16" t="n">
-        <v>6444586</v>
+        <v>6444452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399391</v>
+        <v>113399384</v>
       </c>
       <c r="B17" t="n">
-        <v>56782</v>
+        <v>95624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2547,25 +2547,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318054</v>
+        <v>318059</v>
       </c>
       <c r="R17" t="n">
-        <v>6444671</v>
+        <v>6444586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2611,11 +2611,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,10 +2637,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399393</v>
+        <v>113399385</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>95624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,25 +2649,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2682,10 +2677,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318057</v>
+        <v>318027</v>
       </c>
       <c r="R18" t="n">
-        <v>6444564</v>
+        <v>6444643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,11 +2713,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399386</v>
+        <v>113399393</v>
       </c>
       <c r="B19" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,25 +2751,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2789,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318032</v>
+        <v>318057</v>
       </c>
       <c r="R19" t="n">
-        <v>6444666</v>
+        <v>6444564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2825,6 +2815,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399383</v>
+        <v>113399391</v>
       </c>
       <c r="B20" t="n">
-        <v>95602</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,25 +2858,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317945</v>
+        <v>318054</v>
       </c>
       <c r="R20" t="n">
-        <v>6444452</v>
+        <v>6444671</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2927,6 +2922,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>113258470</v>
       </c>
       <c r="B13" t="n">
-        <v>95624</v>
+        <v>95628</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>113288922</v>
       </c>
       <c r="B14" t="n">
-        <v>56659</v>
+        <v>56661</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399386</v>
+        <v>113399393</v>
       </c>
       <c r="B15" t="n">
-        <v>95624</v>
+        <v>56785</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318032</v>
+        <v>318057</v>
       </c>
       <c r="R15" t="n">
-        <v>6444666</v>
+        <v>6444564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,6 +2407,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,10 +2438,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399383</v>
+        <v>113399391</v>
       </c>
       <c r="B16" t="n">
-        <v>95624</v>
+        <v>56785</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,25 +2450,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2473,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>317945</v>
+        <v>318054</v>
       </c>
       <c r="R16" t="n">
-        <v>6444452</v>
+        <v>6444671</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2509,6 +2514,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2538,7 +2548,7 @@
         <v>113399384</v>
       </c>
       <c r="B17" t="n">
-        <v>95624</v>
+        <v>95628</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2637,10 +2647,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399385</v>
+        <v>113399386</v>
       </c>
       <c r="B18" t="n">
-        <v>95624</v>
+        <v>95628</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2677,10 +2687,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318027</v>
+        <v>318032</v>
       </c>
       <c r="R18" t="n">
-        <v>6444643</v>
+        <v>6444666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2739,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399393</v>
+        <v>113399385</v>
       </c>
       <c r="B19" t="n">
-        <v>56782</v>
+        <v>95628</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2751,25 +2761,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2779,10 +2789,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318057</v>
+        <v>318027</v>
       </c>
       <c r="R19" t="n">
-        <v>6444564</v>
+        <v>6444643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2815,11 +2825,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399391</v>
+        <v>113399383</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>95628</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2858,25 +2863,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318054</v>
+        <v>317945</v>
       </c>
       <c r="R20" t="n">
-        <v>6444671</v>
+        <v>6444452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,11 +2927,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>113411940</v>
       </c>
       <c r="B21" t="n">
-        <v>56657</v>
+        <v>56660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>113258470</v>
       </c>
       <c r="B13" t="n">
-        <v>95628</v>
+        <v>95634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>113288922</v>
       </c>
       <c r="B14" t="n">
-        <v>56661</v>
+        <v>56665</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399393</v>
+        <v>113399384</v>
       </c>
       <c r="B15" t="n">
-        <v>56785</v>
+        <v>95628</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318057</v>
+        <v>318059</v>
       </c>
       <c r="R15" t="n">
-        <v>6444564</v>
+        <v>6444586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,11 +2407,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2545,7 +2540,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399384</v>
+        <v>113399386</v>
       </c>
       <c r="B17" t="n">
         <v>95628</v>
@@ -2585,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318059</v>
+        <v>318032</v>
       </c>
       <c r="R17" t="n">
-        <v>6444586</v>
+        <v>6444666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2647,7 +2642,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399386</v>
+        <v>113399383</v>
       </c>
       <c r="B18" t="n">
         <v>95628</v>
@@ -2687,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318032</v>
+        <v>317945</v>
       </c>
       <c r="R18" t="n">
-        <v>6444666</v>
+        <v>6444452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2851,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399383</v>
+        <v>113399393</v>
       </c>
       <c r="B20" t="n">
-        <v>95628</v>
+        <v>56785</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,25 +2858,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317945</v>
+        <v>318057</v>
       </c>
       <c r="R20" t="n">
-        <v>6444452</v>
+        <v>6444564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2927,6 +2922,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>113411940</v>
       </c>
       <c r="B21" t="n">
-        <v>56660</v>
+        <v>56664</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399384</v>
+        <v>113399385</v>
       </c>
       <c r="B15" t="n">
-        <v>95628</v>
+        <v>95634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318059</v>
+        <v>318027</v>
       </c>
       <c r="R15" t="n">
-        <v>6444586</v>
+        <v>6444643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399391</v>
+        <v>113399383</v>
       </c>
       <c r="B16" t="n">
-        <v>56785</v>
+        <v>95634</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,25 +2445,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318054</v>
+        <v>317945</v>
       </c>
       <c r="R16" t="n">
-        <v>6444671</v>
+        <v>6444452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2509,11 +2509,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2543,7 +2538,7 @@
         <v>113399386</v>
       </c>
       <c r="B17" t="n">
-        <v>95628</v>
+        <v>95634</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2642,10 +2637,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399383</v>
+        <v>113399393</v>
       </c>
       <c r="B18" t="n">
-        <v>95628</v>
+        <v>56789</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2654,25 +2649,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2682,10 +2677,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>317945</v>
+        <v>318057</v>
       </c>
       <c r="R18" t="n">
-        <v>6444452</v>
+        <v>6444564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,6 +2713,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399385</v>
+        <v>113399384</v>
       </c>
       <c r="B19" t="n">
-        <v>95628</v>
+        <v>95634</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318027</v>
+        <v>318059</v>
       </c>
       <c r="R19" t="n">
-        <v>6444643</v>
+        <v>6444586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399393</v>
+        <v>113399391</v>
       </c>
       <c r="B20" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318057</v>
+        <v>318054</v>
       </c>
       <c r="R20" t="n">
-        <v>6444564</v>
+        <v>6444671</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,7 +2331,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399385</v>
+        <v>113399384</v>
       </c>
       <c r="B15" t="n">
         <v>95634</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318027</v>
+        <v>318059</v>
       </c>
       <c r="R15" t="n">
-        <v>6444643</v>
+        <v>6444586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399383</v>
+        <v>113399386</v>
       </c>
       <c r="B16" t="n">
         <v>95634</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>317945</v>
+        <v>318032</v>
       </c>
       <c r="R16" t="n">
-        <v>6444452</v>
+        <v>6444666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399386</v>
+        <v>113399383</v>
       </c>
       <c r="B17" t="n">
         <v>95634</v>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318032</v>
+        <v>317945</v>
       </c>
       <c r="R17" t="n">
-        <v>6444666</v>
+        <v>6444452</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399393</v>
+        <v>113399391</v>
       </c>
       <c r="B18" t="n">
         <v>56789</v>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318057</v>
+        <v>318054</v>
       </c>
       <c r="R18" t="n">
-        <v>6444564</v>
+        <v>6444671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399384</v>
+        <v>113399393</v>
       </c>
       <c r="B19" t="n">
-        <v>95634</v>
+        <v>56789</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318059</v>
+        <v>318057</v>
       </c>
       <c r="R19" t="n">
-        <v>6444586</v>
+        <v>6444564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,6 +2820,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399391</v>
+        <v>113399385</v>
       </c>
       <c r="B20" t="n">
-        <v>56789</v>
+        <v>95634</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2858,25 +2863,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318054</v>
+        <v>318027</v>
       </c>
       <c r="R20" t="n">
-        <v>6444671</v>
+        <v>6444643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,11 +2927,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2076,7 +2076,7 @@
         <v>113258470</v>
       </c>
       <c r="B13" t="n">
-        <v>95634</v>
+        <v>95641</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>113288922</v>
       </c>
       <c r="B14" t="n">
-        <v>56665</v>
+        <v>56672</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399384</v>
+        <v>113399393</v>
       </c>
       <c r="B15" t="n">
-        <v>95634</v>
+        <v>56796</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318059</v>
+        <v>318057</v>
       </c>
       <c r="R15" t="n">
-        <v>6444586</v>
+        <v>6444564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,6 +2407,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,10 +2438,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399386</v>
+        <v>113399384</v>
       </c>
       <c r="B16" t="n">
-        <v>95634</v>
+        <v>95641</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318032</v>
+        <v>318059</v>
       </c>
       <c r="R16" t="n">
-        <v>6444666</v>
+        <v>6444586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2535,10 +2540,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399383</v>
+        <v>113399385</v>
       </c>
       <c r="B17" t="n">
-        <v>95634</v>
+        <v>95641</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>317945</v>
+        <v>318027</v>
       </c>
       <c r="R17" t="n">
-        <v>6444452</v>
+        <v>6444643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2637,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399391</v>
+        <v>113399386</v>
       </c>
       <c r="B18" t="n">
-        <v>56789</v>
+        <v>95641</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2649,25 +2654,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318054</v>
+        <v>318032</v>
       </c>
       <c r="R18" t="n">
-        <v>6444671</v>
+        <v>6444666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2713,11 +2718,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399393</v>
+        <v>113399383</v>
       </c>
       <c r="B19" t="n">
-        <v>56789</v>
+        <v>95641</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318057</v>
+        <v>317945</v>
       </c>
       <c r="R19" t="n">
-        <v>6444564</v>
+        <v>6444452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,11 +2820,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399385</v>
+        <v>113399391</v>
       </c>
       <c r="B20" t="n">
-        <v>95634</v>
+        <v>56796</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,25 +2858,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318027</v>
+        <v>318054</v>
       </c>
       <c r="R20" t="n">
-        <v>6444643</v>
+        <v>6444671</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2927,6 +2922,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>113411940</v>
       </c>
       <c r="B21" t="n">
-        <v>56664</v>
+        <v>56671</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399393</v>
+        <v>113399391</v>
       </c>
       <c r="B15" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318057</v>
+        <v>318054</v>
       </c>
       <c r="R15" t="n">
-        <v>6444564</v>
+        <v>6444671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399384</v>
+        <v>113399393</v>
       </c>
       <c r="B16" t="n">
-        <v>95641</v>
+        <v>56798</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318059</v>
+        <v>318057</v>
       </c>
       <c r="R16" t="n">
-        <v>6444586</v>
+        <v>6444564</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2514,6 +2514,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2540,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399385</v>
+        <v>113399384</v>
       </c>
       <c r="B17" t="n">
-        <v>95641</v>
+        <v>95646</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2580,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318027</v>
+        <v>318059</v>
       </c>
       <c r="R17" t="n">
-        <v>6444643</v>
+        <v>6444586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2642,10 +2647,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399386</v>
+        <v>113399383</v>
       </c>
       <c r="B18" t="n">
-        <v>95641</v>
+        <v>95646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2682,10 +2687,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318032</v>
+        <v>317945</v>
       </c>
       <c r="R18" t="n">
-        <v>6444666</v>
+        <v>6444452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2744,10 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399383</v>
+        <v>113399385</v>
       </c>
       <c r="B19" t="n">
-        <v>95641</v>
+        <v>95646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2784,10 +2789,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>317945</v>
+        <v>318027</v>
       </c>
       <c r="R19" t="n">
-        <v>6444452</v>
+        <v>6444643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2846,10 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399391</v>
+        <v>113399386</v>
       </c>
       <c r="B20" t="n">
-        <v>56796</v>
+        <v>95646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2858,25 +2863,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318054</v>
+        <v>318032</v>
       </c>
       <c r="R20" t="n">
-        <v>6444671</v>
+        <v>6444666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,11 +2927,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,7 +2956,7 @@
         <v>113411940</v>
       </c>
       <c r="B21" t="n">
-        <v>56671</v>
+        <v>56673</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399391</v>
+        <v>113399384</v>
       </c>
       <c r="B15" t="n">
-        <v>56798</v>
+        <v>95674</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318054</v>
+        <v>318059</v>
       </c>
       <c r="R15" t="n">
-        <v>6444671</v>
+        <v>6444586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,11 +2407,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2438,10 +2433,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399393</v>
+        <v>113399383</v>
       </c>
       <c r="B16" t="n">
-        <v>56798</v>
+        <v>95674</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2450,25 +2445,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2478,10 +2473,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318057</v>
+        <v>317945</v>
       </c>
       <c r="R16" t="n">
-        <v>6444564</v>
+        <v>6444452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2514,11 +2509,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2545,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399384</v>
+        <v>113399385</v>
       </c>
       <c r="B17" t="n">
-        <v>95646</v>
+        <v>95674</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2585,10 +2575,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318059</v>
+        <v>318027</v>
       </c>
       <c r="R17" t="n">
-        <v>6444586</v>
+        <v>6444643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2647,10 +2637,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399383</v>
+        <v>113399391</v>
       </c>
       <c r="B18" t="n">
-        <v>95646</v>
+        <v>56826</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2659,25 +2649,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2687,10 +2677,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>317945</v>
+        <v>318054</v>
       </c>
       <c r="R18" t="n">
-        <v>6444452</v>
+        <v>6444671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2723,6 +2713,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399385</v>
+        <v>113399393</v>
       </c>
       <c r="B19" t="n">
-        <v>95646</v>
+        <v>56826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2789,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318027</v>
+        <v>318057</v>
       </c>
       <c r="R19" t="n">
-        <v>6444643</v>
+        <v>6444564</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2825,6 +2820,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,7 +2854,7 @@
         <v>113399386</v>
       </c>
       <c r="B20" t="n">
-        <v>95646</v>
+        <v>95674</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>113411940</v>
       </c>
       <c r="B21" t="n">
-        <v>56673</v>
+        <v>56701</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113399384</v>
+        <v>113399393</v>
       </c>
       <c r="B15" t="n">
-        <v>95674</v>
+        <v>56826</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318059</v>
+        <v>318057</v>
       </c>
       <c r="R15" t="n">
-        <v>6444586</v>
+        <v>6444564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,6 +2407,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,7 +2438,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399383</v>
+        <v>113399386</v>
       </c>
       <c r="B16" t="n">
         <v>95674</v>
@@ -2473,10 +2478,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>317945</v>
+        <v>318032</v>
       </c>
       <c r="R16" t="n">
-        <v>6444452</v>
+        <v>6444666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2535,7 +2540,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399385</v>
+        <v>113399384</v>
       </c>
       <c r="B17" t="n">
         <v>95674</v>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318027</v>
+        <v>318059</v>
       </c>
       <c r="R17" t="n">
-        <v>6444643</v>
+        <v>6444586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2637,10 +2642,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399391</v>
+        <v>113399383</v>
       </c>
       <c r="B18" t="n">
-        <v>56826</v>
+        <v>95674</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2649,25 +2654,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2677,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318054</v>
+        <v>317945</v>
       </c>
       <c r="R18" t="n">
-        <v>6444671</v>
+        <v>6444452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2713,11 +2718,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399393</v>
+        <v>113399385</v>
       </c>
       <c r="B19" t="n">
-        <v>56826</v>
+        <v>95674</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318057</v>
+        <v>318027</v>
       </c>
       <c r="R19" t="n">
-        <v>6444564</v>
+        <v>6444643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,11 +2820,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,10 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399386</v>
+        <v>113399391</v>
       </c>
       <c r="B20" t="n">
-        <v>95674</v>
+        <v>56826</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,25 +2858,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318032</v>
+        <v>318054</v>
       </c>
       <c r="R20" t="n">
-        <v>6444666</v>
+        <v>6444671</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2927,6 +2922,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3206,6 +3206,148 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114894727</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>318099</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6444673</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två par. Observerade + läte. Tydliga vita sträck på vingarna.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -3939,10 +3939,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119852418</v>
+        <v>119852413</v>
       </c>
       <c r="B29" t="n">
-        <v>56221</v>
+        <v>56223</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3955,26 +3955,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119852413</v>
+        <v>119852418</v>
       </c>
       <c r="B30" t="n">
-        <v>56223</v>
+        <v>56221</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4088,26 +4088,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -3939,10 +3939,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119852413</v>
+        <v>119852418</v>
       </c>
       <c r="B29" t="n">
-        <v>56223</v>
+        <v>56221</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3955,26 +3955,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119852418</v>
+        <v>119852413</v>
       </c>
       <c r="B30" t="n">
-        <v>56221</v>
+        <v>56223</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4088,26 +4088,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -3939,10 +3939,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119852418</v>
+        <v>119852413</v>
       </c>
       <c r="B29" t="n">
-        <v>56221</v>
+        <v>56233</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3955,26 +3955,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119852413</v>
+        <v>119852418</v>
       </c>
       <c r="B30" t="n">
-        <v>56223</v>
+        <v>56231</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4088,26 +4088,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -3939,10 +3939,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119852413</v>
+        <v>119852418</v>
       </c>
       <c r="B29" t="n">
-        <v>56233</v>
+        <v>56231</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3955,26 +3955,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119852418</v>
+        <v>119852413</v>
       </c>
       <c r="B30" t="n">
-        <v>56231</v>
+        <v>56233</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4088,26 +4088,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4203,6 +4203,144 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120456959</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56233</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>318110</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6444657</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En aktiv individ längs med skogskanten till naturskog. Jagade en stund längs med kantzonen.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -3814,7 +3814,7 @@
         <v>119018115</v>
       </c>
       <c r="B28" t="n">
-        <v>56266</v>
+        <v>56269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119852413</v>
+        <v>120456959</v>
       </c>
       <c r="B30" t="n">
-        <v>56233</v>
+        <v>56257</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4107,12 +4107,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>registreringar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -4129,17 +4129,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>318099</v>
+        <v>318110</v>
       </c>
       <c r="R30" t="n">
-        <v>6444673</v>
+        <v>6444657</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4163,22 +4163,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En aktiv individ längs med skogskanten till naturskog. Jagade en stund längs med kantzonen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4198,148 +4203,10 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emily Macgregor, Joachim Rosengren</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>120456959</v>
-      </c>
-      <c r="B31" t="n">
-        <v>56257</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Pipistrellus pygmaeus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>318110</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6444657</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Stenungsund</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Ödsmål</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>20:54</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>20:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En aktiv individ längs med skogskanten till naturskog. Jagade en stund längs med kantzonen.</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -1693,12 +1693,7 @@
         <v>103925142</v>
       </c>
       <c r="B10" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>318109.5935356551</v>
+        <v>318110</v>
       </c>
       <c r="R10" t="n">
-        <v>6444656.987985757</v>
+        <v>6444657</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -3814,12 +3809,7 @@
         <v>119018115</v>
       </c>
       <c r="B28" t="n">
-        <v>56269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4198,6 +4198,267 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129162102</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56608</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>318104</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6444672</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129162107</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56613</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>318104</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6444672</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Samtliga registrerade inspelningar från kvällen innehöll typisk spelsång. Samma spellokal som år 2024.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>103925142</v>
       </c>
       <c r="B10" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>119018115</v>
       </c>
       <c r="B28" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>129162102</v>
       </c>
       <c r="B31" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>129162107</v>
       </c>
       <c r="B32" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>103925142</v>
       </c>
       <c r="B10" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>119018115</v>
       </c>
       <c r="B28" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>129162102</v>
       </c>
       <c r="B31" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>129162107</v>
       </c>
       <c r="B32" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -1693,7 +1693,7 @@
         <v>103925142</v>
       </c>
       <c r="B10" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>119018115</v>
       </c>
       <c r="B28" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>129162102</v>
       </c>
       <c r="B31" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>129162107</v>
       </c>
       <c r="B32" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103929502</v>
+        <v>113258470</v>
       </c>
       <c r="B2" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräcke Skog, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318111.0512606705</v>
+        <v>318022</v>
       </c>
       <c r="R2" t="n">
-        <v>6444619.348339278</v>
+        <v>6444680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,63 +795,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103929414</v>
+        <v>113399383</v>
       </c>
       <c r="B3" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318055.7241663652</v>
+        <v>317945</v>
       </c>
       <c r="R3" t="n">
-        <v>6444661.57169356</v>
+        <v>6444452</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,75 +880,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103929399</v>
+        <v>113399384</v>
       </c>
       <c r="B4" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräcke Skog, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318092.6183516062</v>
+        <v>318059</v>
       </c>
       <c r="R4" t="n">
-        <v>6444575.73945565</v>
+        <v>6444586</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,78 +977,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104143042</v>
+        <v>113399385</v>
       </c>
       <c r="B5" t="n">
-        <v>56437</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100054</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pilgrimsfalk</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Falco peregrinus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tunstall, 1771</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smällen, Stora Hällungen, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>318123.9910739388</v>
+        <v>318027</v>
       </c>
       <c r="R5" t="n">
-        <v>6444624.047863641</v>
+        <v>6444643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,27 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förbiflygande individ observerad med kikare från fönstret. Individen flög sydväst mot skogsområde.</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,81 +1070,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Öppen hagmark omgiven av blandskog och barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103929490</v>
+        <v>113399386</v>
       </c>
       <c r="B6" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>318107.8583322791</v>
+        <v>318032</v>
       </c>
       <c r="R6" t="n">
-        <v>6444642.249996905</v>
+        <v>6444666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,22 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,27 +1171,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105152530</v>
+        <v>113399387</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,54 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>318098.6550463591</v>
+        <v>318021</v>
       </c>
       <c r="R7" t="n">
-        <v>6444672.835431137</v>
+        <v>6444698</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,22 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,49 +1268,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105152512</v>
+        <v>113325904</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1468,29 +1313,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>318103.3925640297</v>
+        <v>318016</v>
       </c>
       <c r="R8" t="n">
-        <v>6444672.089307204</v>
+        <v>6444685</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1517,22 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,6 +1370,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1559,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108587811</v>
+        <v>113411940</v>
       </c>
       <c r="B9" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1597,34 +1422,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Boh</t>
+          <t>Smällen, Stora Hällungen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318094.8760329307</v>
+        <v>318125</v>
       </c>
       <c r="R9" t="n">
-        <v>6444659.778670337</v>
+        <v>6444624</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1648,22 +1464,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Duvhök attackerad av skata och nötskrika. Flög upp i skogen igen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103925142</v>
+        <v>111492972</v>
       </c>
       <c r="B10" t="n">
-        <v>56620</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,47 +1522,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206000</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+          <t>Smällen, Smällen, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>318110</v>
+        <v>317936</v>
       </c>
       <c r="R10" t="n">
-        <v>6444657</v>
+        <v>6444436</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1765,22 +1590,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,31 +1620,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Joachim Rosengren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Joachim Rosengren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111492972</v>
+        <v>113399390</v>
       </c>
       <c r="B11" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1840,34 +1660,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Smällen (Smällen), Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317936.710894453</v>
+        <v>318099</v>
       </c>
       <c r="R11" t="n">
-        <v>6444436.289034157</v>
+        <v>6444698</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1891,22 +1697,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,27 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joachim Rosengren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joachim Rosengren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112715667</v>
+        <v>113399391</v>
       </c>
       <c r="B12" t="n">
-        <v>57939</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,54 +1745,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100141</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>318039</v>
+        <v>318054</v>
       </c>
       <c r="R12" t="n">
-        <v>6444657</v>
+        <v>6444671</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2020,27 +1799,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hittade en individ i skogsmiljö. Troligen letade den efter en lämplig övervintringsplats.</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,34 +1818,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113258470</v>
+        <v>113399393</v>
       </c>
       <c r="B13" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,46 +1847,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>318022</v>
+        <v>318057</v>
       </c>
       <c r="R13" t="n">
-        <v>6444680</v>
+        <v>6444563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2150,22 +1901,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2174,56 +1920,50 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113288922</v>
+        <v>104143042</v>
       </c>
       <c r="B14" t="n">
-        <v>57158</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6046616</v>
+        <v>100054</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvhök, underarten buteoides</t>
+          <t>Pilgrimsfalk</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accipiter gentilis buteoides</t>
+          <t>Falco peregrinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Menzbier, 1882)</t>
+          <t>Tunstall, 1771</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2235,7 +1975,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2245,17 +1985,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Smällen, Stora Hällungen, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>318075</v>
+        <v>318125</v>
       </c>
       <c r="R14" t="n">
-        <v>6444616</v>
+        <v>6444624</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2279,27 +2019,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>utsträckt huvud, flygande, rak stjärt.</t>
+          <t>Förbiflygande individ observerad med kikare från fönstret. Individen flög sydväst mot skogsområde.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2310,6 +2050,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Öppen hagmark omgiven av blandskog och barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2326,15 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113332687</v>
+        <v>108502212</v>
       </c>
       <c r="B15" t="n">
-        <v>57792</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,16 +2082,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102990</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2361,30 +2101,25 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318072</v>
+        <v>318141</v>
       </c>
       <c r="R15" t="n">
-        <v>6444670</v>
+        <v>6444571</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2411,22 +2146,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,15 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113399397</v>
+        <v>115283425</v>
       </c>
       <c r="B16" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,16 +2199,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2486,20 +2216,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke Skog, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318035</v>
+        <v>318082</v>
       </c>
       <c r="R16" t="n">
-        <v>6444683</v>
+        <v>6444552</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2523,12 +2267,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2543,27 +2287,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113399385</v>
+        <v>103929502</v>
       </c>
       <c r="B17" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2571,34 +2310,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke Skog, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318027</v>
+        <v>318112</v>
       </c>
       <c r="R17" t="n">
-        <v>6444643</v>
+        <v>6444619</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2625,12 +2374,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,65 +2394,74 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113399391</v>
+        <v>117716656</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100092</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318054</v>
+        <v>317936</v>
       </c>
       <c r="R18" t="n">
-        <v>6444671</v>
+        <v>6444436</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2727,17 +2485,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,27 +2505,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Joachim Rosengren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Joachim Rosengren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113399386</v>
+        <v>119852418</v>
       </c>
       <c r="B19" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,37 +2528,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100111</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke skog, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318032</v>
+        <v>318099</v>
       </c>
       <c r="R19" t="n">
-        <v>6444666</v>
+        <v>6444673</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2834,12 +2603,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,27 +2633,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor, Joachim Rosengren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113399383</v>
+        <v>120547261</v>
       </c>
       <c r="B20" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2882,37 +2656,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>100111</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317945</v>
+        <v>318097</v>
       </c>
       <c r="R20" t="n">
-        <v>6444452</v>
+        <v>6444647</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2936,12 +2731,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Trollpipistrell sonar tillsammans med spelläte av gråskimlig fladdermus</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,65 +2766,81 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113399393</v>
+        <v>112124478</v>
       </c>
       <c r="B21" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100141</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke Skog 540, Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>318057</v>
+        <v>318084</v>
       </c>
       <c r="R21" t="n">
-        <v>6444563</v>
+        <v>6444639</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3038,17 +2864,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Försökte troligen övervintra i trappen. Tros komma från intilliggande skog i väst med sumpskogskaraktär</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3057,33 +2893,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113399384</v>
+        <v>112715667</v>
       </c>
       <c r="B22" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,37 +2923,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2569</v>
+        <v>100141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke skog, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>318059</v>
+        <v>318039</v>
       </c>
       <c r="R22" t="n">
-        <v>6444586</v>
+        <v>6444657</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3145,12 +2994,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hittade en individ i skogsmiljö. Troligen letade den efter en lämplig övervintringsplats.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3159,55 +3023,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113411940</v>
+        <v>120257313</v>
       </c>
       <c r="B23" t="n">
-        <v>57156</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100001</v>
+        <v>100141</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3215,7 +3075,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3223,17 +3092,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Smällen, Stora Hällungen, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>318125</v>
+        <v>318101</v>
       </c>
       <c r="R23" t="n">
-        <v>6444624</v>
+        <v>6444613</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3257,27 +3126,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Duvhök attackerad av skata och nötskrika. Flög upp i skogen igen.</t>
+          <t>Påväg till övervintringsplats</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3304,32 +3173,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114449041</v>
+        <v>111272831</v>
       </c>
       <c r="B24" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3337,33 +3201,18 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Smällen, Smällen, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>318104</v>
+        <v>318098</v>
       </c>
       <c r="R24" t="n">
-        <v>6444672</v>
+        <v>6444620</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3390,22 +3239,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,15 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114894727</v>
+        <v>109096722</v>
       </c>
       <c r="B25" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,57 +3292,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>102980</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>318099</v>
+        <v>318101</v>
       </c>
       <c r="R25" t="n">
-        <v>6444673</v>
+        <v>6444613</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3522,27 +3351,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Två par. Observerade + läte. Tydliga vita sträck på vingarna.</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3553,11 +3377,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3574,37 +3393,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115283425</v>
+        <v>108221715</v>
       </c>
       <c r="B26" t="n">
-        <v>56611</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100065</v>
+        <v>102987</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3612,26 +3426,22 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>i par</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bräcke Skog, Stenungsund, Boh</t>
+          <t>Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>318082</v>
+        <v>318080</v>
       </c>
       <c r="R26" t="n">
-        <v>6444552</v>
+        <v>6444656</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3658,12 +3468,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3690,47 +3510,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117716656</v>
+        <v>113332687</v>
       </c>
       <c r="B27" t="n">
-        <v>56198</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100092</v>
+        <v>102990</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3740,17 +3556,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317936</v>
+        <v>318072</v>
       </c>
       <c r="R27" t="n">
-        <v>6444436</v>
+        <v>6444670</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3774,12 +3590,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3794,22 +3620,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joachim Rosengren</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joachim Rosengren</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119018115</v>
+        <v>108221741</v>
       </c>
       <c r="B28" t="n">
-        <v>56620</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,58 +3643,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>206000</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bräcke Skog, Boh</t>
+          <t>Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>318060</v>
+        <v>318084</v>
       </c>
       <c r="R28" t="n">
-        <v>6444678</v>
+        <v>6444644</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3892,17 +3707,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Återkommande gråskimlig fladdermus med socialt läte. Troligt revir vid skogsmiljö.</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3929,15 +3749,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119852418</v>
+        <v>109307737</v>
       </c>
       <c r="B29" t="n">
-        <v>56231</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3945,58 +3760,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100111</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>318099</v>
+        <v>318085</v>
       </c>
       <c r="R29" t="n">
-        <v>6444673</v>
+        <v>6444651</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4020,22 +3824,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4055,22 +3859,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emily Macgregor, Joachim Rosengren</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120456959</v>
+        <v>113399397</v>
       </c>
       <c r="B30" t="n">
-        <v>56257</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4078,58 +3877,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205995</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>318110</v>
+        <v>318035</v>
       </c>
       <c r="R30" t="n">
-        <v>6444657</v>
+        <v>6444683</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4153,27 +3931,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>20:54</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>20:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En aktiv individ längs med skogskanten till naturskog. Jagade en stund längs med kantzonen.</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4188,22 +3951,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129162102</v>
+        <v>108587811</v>
       </c>
       <c r="B31" t="n">
-        <v>56615</v>
+        <v>58439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4211,58 +3974,56 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205995</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Bräcke Skog 540, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>318104</v>
+        <v>318094</v>
       </c>
       <c r="R31" t="n">
-        <v>6444672</v>
+        <v>6444660</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4286,22 +4047,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4328,69 +4089,58 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129162107</v>
+        <v>103929414</v>
       </c>
       <c r="B32" t="n">
-        <v>56620</v>
+        <v>58112</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>206000</v>
+        <v>103020</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bräcke skog, Boh</t>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>318104</v>
+        <v>318056</v>
       </c>
       <c r="R32" t="n">
-        <v>6444672</v>
+        <v>6444662</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4414,27 +4164,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>22:10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Samtliga registrerade inspelningar från kvällen innehöll typisk spelsång. Samma spellokal som år 2024.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4458,6 +4203,4101 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114894727</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>318099</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6444673</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Två par. Observerade + läte. Tydliga vita sträck på vingarna.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>107996586</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>318082</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6444648</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>109307651</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>318093</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6444648</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114465830</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>318087</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6444643</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>107765115</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>318097</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6444647</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114449041</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>318104</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6444672</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>103929399</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bräcke Skog, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>318093</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6444576</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>105152512</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>318104</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6444672</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115893251</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>318097</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6444647</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115970028</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>318093</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6444648</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>119064845</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bräcke Skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>318101</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6444628</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>105152530</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>318099</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6444673</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115739469</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>318077</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6444630</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Två inspelningar totalt under kvällen, 21:08 och 21:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>119929469</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>318093</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6444648</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120456959</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>318110</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6444657</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En aktiv individ längs med skogskanten till naturskog. Jagade en stund längs med kantzonen.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120547224</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>318097</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6444647</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129162102</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>318104</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6444672</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>103929490</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>318108</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6444642</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>116633850</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>318093</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6444648</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>103925142</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>318110</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6444657</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115900216</v>
+      </c>
+      <c r="B53" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>318097</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6444647</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Granskad av Johanna Kammonen enligt minimikraven</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>119018115</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bräcke Skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>318060</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6444678</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Återkommande gråskimlig fladdermus med socialt läte. Troligt revir vid skogsmiljö.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120215539</v>
+      </c>
+      <c r="B55" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>318077</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6444630</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Hörbart socialt tickande spelljud/revirläte av gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120259788</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>318080</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6444642</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Revirläte socialt av gråskimlig fladdermus. Återkommande. Har spelats in på samma plats tidigare.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120456897</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>318096</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6444653</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Revirhävdande individ intill kantzon mellan naturskog och en mindre yta öppen gräsmark som kantas av en trädridå. Individ aktiv i lite mer än en timma.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129162107</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Boh</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>318104</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6444672</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Samtliga registrerade inspelningar från kvällen innehöll typisk spelsång. Samma spellokal som år 2024.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>115892919</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>318085</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6444651</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>119929467</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Boh</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>318093</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6444648</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Emily Macgregor, Joachim Rosengren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>104140919</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>318070</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6444646</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>103929451</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>318077</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6444630</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>103929456</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 540, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>318086</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6444626</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>116117901</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>318168</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6444641</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulf Nilsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulf Nilsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>113288922</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6046616</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Duvhök, underarten buteoides</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Astur gentilis buteoides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Menzbier, 1882)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>318075</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6444616</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>utsträckt huvud, flygande, rak stjärt.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -7326,7 +7326,7 @@
         <v>129162107</v>
       </c>
       <c r="B58" t="n">
-        <v>56840</v>
+        <v>56859</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 46487-2023 artfynd.xlsx
+++ b/artfynd/A 46487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399383</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399384</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399385</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399386</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399387</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113325904</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411940</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492972</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399391</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399393</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104143042</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108502212</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283425</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103929502</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117716656</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2642,6 +2732,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852418</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2775,6 +2870,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120547261</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2909,6 +3009,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112124478</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3039,6 +3144,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112715667</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3170,6 +3280,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120257313</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3278,6 +3393,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111272831</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3390,6 +3510,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109096722</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3507,6 +3632,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108221715</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3629,6 +3759,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113332687</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3746,6 +3881,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108221741</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3863,6 +4003,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109307737</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3960,6 +4105,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399397</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4086,6 +4236,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108587811</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4203,6 +4358,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103929414</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4340,6 +4500,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114894727</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4452,6 +4617,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107996586</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4564,6 +4734,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109307651</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4686,6 +4861,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114465830</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4803,6 +4983,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107765115</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4926,6 +5111,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114449041</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5043,6 +5233,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103929399</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5157,6 +5352,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105152512</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5285,6 +5485,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115893251</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5413,6 +5618,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115970028</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5541,6 +5751,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064845</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5655,6 +5870,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105152530</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5788,6 +6008,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115739469</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5916,6 +6141,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119929469</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6049,6 +6279,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456959</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6177,6 +6412,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120547224</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6305,6 +6545,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129162102</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6412,6 +6657,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103929490</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6540,6 +6790,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633850</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6657,6 +6912,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103925142</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6800,6 +7060,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115900216</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6923,6 +7188,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018115</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7054,6 +7324,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215539</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7187,6 +7462,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120259788</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7320,6 +7600,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120456897</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7453,6 +7738,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129162107</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7581,6 +7871,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115892919</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7709,6 +8004,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119929467</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7816,6 +8116,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104140919</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7937,6 +8242,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103929451</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8058,6 +8368,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103929456</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8170,6 +8485,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116117901</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8298,8 +8618,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113288922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>